--- a/avito.xlsx
+++ b/avito.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ИИ-решения, нейросети" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Психология" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Профессии и бизнес" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Консультирование" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Другое" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ИИ-решения, нейросети" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Психология" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Профессии и бизнес" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Консультирование" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -424,12 +425,12 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
@@ -443,8 +444,6 @@
     <col width="18" customWidth="1" min="22" max="22"/>
     <col width="18" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
-    <col width="18" customWidth="1" min="25" max="25"/>
-    <col width="18" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,79 +474,79 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ServiceSubspecies</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>ImageUrls</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>ImageUrls</t>
+          <t>ContactMethod</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>ContactMethod</t>
+          <t>CertificateAfterTraining</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>AIDirection</t>
+          <t>Classes</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Consultations</t>
+          <t>CourseLasts</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>ContentFormat</t>
+          <t>EmploymentAfterTraining</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>InstallmentPayment</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>InternetCalls</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>Place</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>PostInstallationSupport</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Prepayment</t>
-        </is>
-      </c>
       <c r="U1" t="inlineStr">
         <is>
           <t>PriceList</t>
@@ -555,27 +554,17 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>TakeUrgentOrders</t>
+          <t>StartingPrice</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
+          <t>Teacher</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>WorkExperience</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>WorkWith</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>WorkWithContract</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>WorkingWithAI</t>
         </is>
       </c>
     </row>
@@ -597,25 +586,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Деловые услуги</t>
+          <t>Обучение, курсы</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>IT, дизайн, тексты</t>
+          <t>Другое</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ИИ-решения, нейросети</t>
+          <t>Обучение работе с ИИ: ChatGPT, Claude, Codex</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>Обучение работе с ИИ: ChatGPT, Claude, Codex</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
         <is>
           <t>Привет 👋 Меня зовут Лев, мне 26 лет, я консультант по внедрению ИИ. Пользуюсь нейросетями почти каждый день с 2022 года, и на работе, и дома.
 Работаю с двумя сильнейшими моделями на рынке: ChatGPT (включая Codex) и Claude (включая Claude Code). Помогаю встроить их в работу очень конкретно и понятным языком, без лишних терминов.
@@ -640,64 +624,69 @@
 Онлайн по всей России, в Петербурге можно очно.</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>Санкт-Петербург, улица Мира</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, улица Мира</t>
+          <t>https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/portrait-main.jpg</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/portrait-main.jpg | https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/expo-main.jpg</t>
+          <t>По телефону и в сообщениях</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Установка и настройка нейросетей</t>
+          <t>Индивидуальные</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Есть</t>
+          <t>Меньше месяца</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Текст | Изображения, фото | Презентация</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Работа с базой знаний | Формирование отчётов и аналитики</t>
+          <t>Онлайн с преподавателем</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Новички</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>Удалённо | У клиента</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Возможна</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Нужна</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -715,348 +704,215 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>4–7 лет</t>
+          <t>Мужчина</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Физические лица | ИП | ООО</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Да</t>
+          <t>4–6 лет</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ai-01-nastroika-pod-biznes</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ServiceType</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ServiceSubtype</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ServiceSubspecies</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ImageUrls</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ContactMethod</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>AIDirection</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Consultations</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ContentFormat</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>InternetCalls</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Place</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>PostInstallationSupport</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Prepayment</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>PriceList</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>TakeUrgentOrders</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>WorkExperience</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>WorkWith</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>WorkWithContract</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>WorkingWithAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ai-03-studii-dizaina</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>Предложение услуг</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Деловые услуги</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>IT, дизайн, тексты</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>ИИ-решения, нейросети</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Настрою нейросети под задачи вашего бизнеса</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Подписка на ChatGPT оплачена, пару раз она даже помогла с текстом. А времени как не хватало, так и не хватает, и денег она пока не приносит. Знакомо? Так у большинства, кто попробовал нейросети сам.
-Привет, я Лев, консультант по внедрению ИИ. Пользуюсь нейросетями каждый день с 2022 года и помогаю бизнесу превратить «иногда помогает» в инструмент, который делает конкретную работу и делает её одинаково хорошо каждый раз.
-Как проходит встреча
-Берём одну вашу реальную задачу, ту, что съедает больше всего времени. Разбираем, из чего она состоит и какую часть можно отдать нейросети. Тут же собираем под неё промпт и проверяем на ваших данных. Правим, пока результат не станет стабильным. Вы уходите с готовым инструментом и короткой памяткой, как им пользоваться.
-Что обычно отдают нейросети
-Сбор информации о клиенте из переписок и файлов в одну карточку. Первичные ответы на типовые вопросы, которые вы пишете руками по десять раз в день. Отчёты: выгрузка на входе, готовая сводка на выходе. Тексты, презентации и картинки в едином стиле. Разбор больших массивов данных, до которых не доходят руки.
-С чем работаю
-ChatGPT (включая Codex) и Claude (включая Claude Code). Подбираю под задачу, а не по моде. Часто подписка за 20 долларов закрывает то, ради чего люди собираются заказывать дорогую разработку.
-Про честность
-Если вижу, что задача нейросетью решается плохо, говорю сразу, до оплаты. Половина пользы консультации в том, чтобы вы не потратили месяц на то, что пока не работает.
-Кому подходит
-Владельцам небольших компаний и агентств, ИП, руководителям отделов. Работаю и с физлицами, и с юрлицами: по договору, чек как самозанятый.
-Как начать
-Напишите пару слов о задаче. Первые 20 минут бесплатно: разберём запрос, и я честно скажу, есть ли здесь работа для нейросети. Дальше по вашему решению.
-Онлайн по всей России, в Петербурге можно встретиться очно.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Сенная площадь</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/portrait-main.jpg | https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/expo-main.jpg</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Установка и настройка нейросетей</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Текст | Изображения, фото | Презентация</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Работа с базой знаний | Формирование отчётов и аналитики | Презентация товаров или услуг</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Удалённо | У клиента</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Возможна</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Нужна</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Своя услуга|Диагностика 30 минут|1500||за услугу
-Своя услуга|Рабочая встреча 90 минут|4500||за услугу
-Своя услуга|Пакет из 3 встреч|12000||за услугу
-Своя услуга|Сопровождение на месяц|15000||за услугу
-Своя услуга|Внедрение в команду|15000|Да|за услугу</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>4–7 лет</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Физические лица | ИП | ООО</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ai-02-vnedrenie-v-komandu</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Деловые услуги</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>IT, дизайн, тексты</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ИИ-решения, нейросети</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Внедрение ИИ в работу команды</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Внедрение ИИ в команду это не «купили всем подписку и разослали инструкцию». Через месяц после такого внедрения нейросетью пользуются двое из десяти, и то для писем.
-Я делаю иначе: перестраиваю конкретный рабочий процесс так, чтобы нейросеть стала его частью, и учу команду на её собственных задачах. Результат внедрения не скрипт, который где-то крутится, а то, что ваши люди после него делают иначе.
-Как это устроено
-Интервью, 30 минут, бесплатно. Смотрим процессы и ищем, где нейросеть даст заметную экономию времени, а где только отвлечёт.
-Разбор процесса. Раскладываю выбранный процесс на шаги и показываю, какие уходят машине целиком, какие частично, а какие трогать не надо.
-Сборка инструментов. Собираю систему промптов под ваши задачи. Не один универсальный запрос, а набор: под каждую типовую задачу свой, плюс маршрутизация. Сотрудник пишет, что ему нужно, и нужный инструмент подключается сам.
-Обучение команды. Встреча с сотрудниками на их задачах, разбор ошибок. Заранее прохожу материалы с одним человеком из команды, чтобы к общей встрече внутри уже был тот, кто всё проверил руками.
-Документы. Памятка сотрудника, инструкция по настройке аккаунтов и документ с направлениями развития: куда двигаться дальше без меня.
-Пример из практики
-Студия дизайна интерьеров, команда из пяти человек. Главная боль: точечно поправить готовое изображение, не разрушив остальное. Собрал систему из трёх промптов: генерация сцены по коллажу, локальная правка одного элемента, улучшение качества без изменения содержания. Сверху маршрутизирующий файл. Команда получила памятку, инструкцию по настройке и разбор направлений развития.
-Сколько стоит
-От 15 000 ₽ за один процесс и команду до пяти человек. Больше процессов или людей считаем после бесплатного интервью. Работаю по договору, чек как самозанятый.
-Что нужно от вас
-Полтора-два часа на интервью и разбор, доступ к примерам реальных задач и один человек в команде, готовый попробовать первым.
-Онлайн по всей России, в Петербурге можно очно.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Сенная площадь</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/expo-main.jpg | https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/portrait-main.jpg</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Разработка и внедрение ИИ-решений в бизнес</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Текст | Изображения, фото | Презентация</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Работа с базой знаний | Формирование отчётов и аналитики | Консультация клиентов</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Удалённо | У клиента</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Возможна</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Нужна</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Своя услуга|Внедрение в команду|15000|Да|за услугу
-Своя услуга|Консультация 90 минут|4500||за услугу
-Своя услуга|Сопровождение на месяц|15000||за услугу</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>4–7 лет</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>ИП | ООО | Другие юридические лица</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ai-03-studii-dizaina</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Деловые услуги</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>IT, дизайн, тексты</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ИИ-решения, нейросети</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Нейросети для студий дизайна интерьеров</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Узкая тема: нейросети в работе студии дизайна интерьеров. Не «ИИ для бизнеса вообще», а ваш процесс от коллажа с референсами до картинки, которую не стыдно показать заказчику.
 Три задачи, с которыми ко мне приходят студии
@@ -1076,275 +932,131 @@
 Онлайн по всей России, в Петербурге можно очно.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Санкт-Петербург, Сенная площадь</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/expo-main.jpg | https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/portrait-main.jpg</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/expo-main.jpg</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Разработка и внедрение ИИ-решений в бизнес</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Есть</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Изображения, фото | Текст | Презентация</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Презентация товаров или услуг | Работа с базой знаний</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Удалённо | У клиента</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Возможна</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Нужна</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Своя услуга|Внедрение в студию|15000|Да|за услугу
 Своя услуга|Разбор одной задачи 90 минут|4500||за услугу
 Своя услуга|Сопровождение на месяц|15000||за услугу</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>4–7 лет</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>ИП | ООО | Физические лица</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ai-04-rukovoditelu</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ai-05-audit-protsessov</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Предложение услуг</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Деловые услуги</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>IT, дизайн, тексты</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>ИИ-решения, нейросети</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ИИ-консультация для руководителя лично</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Ситуация, которую вижу чаще всего. Руководитель слышал, что нейросети это сильно. Попробовал сам, получилось невнятно. В итоге просит кого-то из сотрудников, кто «немного умеет», сделать отчёт или подобрать материал. Получается медленно, через посредника, и каждый раз надо объяснять заново.
-Я убираю посредника. После консультации вы работаете с нейросетью напрямую, на своих задачах, а не на учебных примерах.
-Как проходит
-Разбираем ваши настоящие рабочие задачи. Показываю, где нейросеть даёт выигрыш уже сегодня: разбор больших массивов данных, подготовка презентаций и идей для собственников, черновики решений, быстрый анализ документов. Настраиваем аккаунт и делаем несколько заходов вместе, пока результат не станет предсказуемым.
-Из практики
-Работал так с директором по продажам крупной российской компании, около 500 человек. Запрос был размытый: «слышал, что это что-то мощное». Начали с базы, убрали посредника в виде коллеги, перешли на прямую работу с подпиской за 20 долларов. Дальше разобрали глубокие исследования и типы данных, с которыми можно работать. Сейчас он на сопровождении, движемся в сторону Codex.
-Формат
-Диагностика 30 минут, 1 500 ₽. Смотрим задачи, честно говорю, стоит ли идти дальше.
-Консультация 90 минут, 4 500 ₽. Разбираем и настраиваем на ваших материалах.
-Пакет из трёх встреч, 12 000 ₽. Когда задач больше одной и нужен результат, а не знакомство.
-Сопровождение на месяц, 15 000 ₽. Регулярные созвоны, новые инструменты по мере готовности.
-Без домашних заданий на двадцать часов и без лекций про то, как нейросети меняют мир. Только то, что вы завтра примените в работе.
-По договору, чек как самозанятый. Онлайн по всей России, в Петербурге можно очно.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Сенная площадь</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/portrait-main.jpg | https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/expo-main.jpg</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Установка и настройка нейросетей</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Текст | Презентация</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Формирование отчётов и аналитики | Презентация товаров или услуг | Работа с базой знаний</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Удалённо | У клиента</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Возможна</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Нужна</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Своя услуга|Диагностика 30 минут|1500||за услугу
-Своя услуга|Консультация 90 минут|4500||за услугу
-Своя услуга|Пакет из 3 встреч|12000||за услугу
-Своя услуга|Сопровождение на месяц|15000||за услугу</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>4–7 лет</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Физические лица | ИП | ООО</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ai-05-audit-protsessov</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Деловые услуги</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>IT, дизайн, тексты</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ИИ-решения, нейросети</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Найду 3–5 процессов, где ИИ сэкономит деньги</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Все уже попробовали ИИ. Подписки куплены, кто-то в команде что-то генерирует, а время не экономится и денег это не приносит. Внедрять «везде» дорого и бесполезно: половина процессов нейросети не по зубам, зато на другой половине она окупается за неделю. Вопрос только в том, какие процессы ваши.
 Я нахожу их за одну встречу. На выходе не «рекомендации по цифровизации», а список из 3–5 конкретных процессов, где ИИ сэкономит вам деньги или время, и план, с чего начать на этой неделе.
@@ -1363,241 +1075,94 @@
 Онлайн по всей России, в Петербурге можно очно.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>9000</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Санкт-Петербург, Сенная площадь</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/expo-main.jpg | https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/portrait-main.jpg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/expo-close.jpg</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Разработка и внедрение ИИ-решений в бизнес</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Есть</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Текст | Презентация</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Формирование отчётов и аналитики | Работа с базой знаний | Приём и обработка заявок</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Удалённо | У клиента</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Возможна</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Нужна</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Своя услуга|Разбор бизнеса: 3–5 процессов для ИИ, с письменным планом|9000||за услугу
 Своя услуга|Консультация 90 минут|4500||за услугу
 Своя услуга|Внедрение в команду|15000|Да|за услугу</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>4–7 лет</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>ИП | ООО | Физические лица</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>life-01-povsednevnye-zadachi</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Деловые услуги</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>IT, дизайн, тексты</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ИИ-решения, нейросети</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ChatGPT для повседневных задач: научу за вечер</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Пришло письмо из налоговой на трёх страницах, и непонятно, что от вас хотят. Надо составить претензию управляющей компании, а с чего начать, неясно. Ребёнок просит помочь с сочинением, а вы после работы. Анализы на руках, до врача неделя, а в интернете один ужас.
-Всё это уже давно умеет делать нейросеть, если знать, как её спросить. Этому я и учу 👋
-Меня зовут Лев, мне 26, я консультант по внедрению ИИ. Пользуюсь нейросетями каждый день с 2022 года, на работе и дома. Объясняю конкретно и понятным языком, без терминов.
-Что разберём за встречу
-Настроим ваш ChatGPT или Claude: регистрация, нужна ли платная версия (чаще всего нет), как не поймать блокировку. Возьмём вашу настоящую задачу, письмо, документ, план или вопрос, и решим её вместе прямо на встрече. Научу главному: как формулировать запрос, чтобы ответ был полезным, и как проверять, что нейросеть не выдумала. Соберём три-четыре заготовки под задачи, которые у вас повторяются.
-С чем обычно приходят
-Письма и заявления в инстанции. Разобраться в договоре, справке, инструкции. Подготовиться к разговору с врачом, работодателем, банком: вопросы и аргументы. Учёба своя и детская: объяснить тему, проверить работу, подготовиться к экзамену. Спланировать поездку, ремонт, бюджет. Перевести, пересказать, сократить. Придумать поздравление, когда слов нет.
-Про здоровье отдельно. Нейросеть не ставит диагнозы, и я тоже. Но она хорошо помогает понять, что написано в анализах, и подготовить вопросы к врачу, чтобы приём прошёл с пользой.
-Как проходит
-Онлайн, по видеосвязи, вдвоём. Вы делаете сами, я подсказываю. Конспект не нужен: вы уходите с настроенным аккаунтом, решённой задачей и заготовками.
-Цены
-Первая встреча 30 минут, 1 500 ₽: посмотрим, что вам нужно, и попробуем на вашей задаче.
-Встреча 90 минут, 4 500 ₽.
-Пакет из трёх встреч, 12 000 ₽, если хочется дойти до уверенности.
-Чек как самозанятый.
-Напишите пару слов, с чем хотите разобраться. Отвечу честно, поможет ли здесь нейросеть 🙂
-*Не консультирую по генерации видео.
-Онлайн по всей России, в Петербурге можно встретиться очно.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, улица Мира</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/portrait-close.jpg | https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/portrait-main.jpg</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Установка и настройка нейросетей</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Текст | Изображения, фото</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Работа с базой знаний | Консультация клиентов</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Удалённо | У клиента</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Возможна</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Нужна</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Своя услуга|Первая встреча 30 минут|1500||за услугу
-Своя услуга|Встреча 90 минут|4500||за услугу
-Своя услуга|Пакет из 3 встреч|12000||за услугу</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>4–7 лет</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Физические лица</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
@@ -1608,7 +1173,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1837,13 +1402,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2027,7 +1592,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>edu-01-s-nulya</t>
+          <t>edu-02-dlya-raboty</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2047,170 +1612,10 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Обучение нейросетям с нуля: ChatGPT и Claude</t>
+          <t>Нейросети для офисной работы: ChatGPT и Claude</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
-        <is>
-          <t>Если вы открывали ChatGPT, получили странный ответ и закрыли, вы не одни. Дело почти всегда не в вас, а в том, что никто не показал, как с ним разговаривать 🙂
-Привет, я Лев, мне 26, консультант по внедрению ИИ. Занимаюсь с людьми, которые начинают с нуля. Никакого программирования, никаких терминов. Показываю на ваших задачах: рабочих, учебных, бытовых, любых, которые вам правда нужны.
-Что разберём на первой встрече
-Какие нейросети сейчас есть и чем они отличаются. Коротко и по делу, без «топ-50 сервисов». Нужно ли вам платить и за что: часто бесплатной версии хватает, а иногда подписка за 20 долларов экономит несколько часов в неделю. Как формулировать запрос, чтобы ответ был полезным с первого раза. Как проверять, что нейросеть не выдумала, это важнее всего остального. И сразу настроим ваш аккаунт и решим одну вашу настоящую задачу.
-С чем ко мне приходят
-Написать письмо или текст, который давно откладывается. Разобраться в документе или договоре. Подготовиться к разговору. Разложить по полочкам таблицу, отчёт, кучу заметок. Придумать идеи и не смотреть в пустой экран. Помочь ребёнку с учёбой. Разобраться со здоровьем и анализами, аккуратно и без диагнозов.
-Как проходит
-Онлайн, вдвоём, по видеосвязи с показом экрана. Вы делаете сами, я рядом подсказываю. Записывать ничего не надо: вы уходите с настроенным аккаунтом и своей решённой задачей.
-Сколько стоит
-Первая встреча 30 минут, 1 500 ₽: посмотрим, что вам вообще нужно, и попробуем. Полноценное занятие 90 минут, 4 500 ₽. Пакет из трёх занятий, 12 000 ₽, если хочется дойти до уверенного уровня.
-Напишите пару слов о том, зачем вам нейросети, и я отвечу, чем реально смогу помочь, а чем нет.
-Онлайн по всей России, в Петербурге можно встретиться очно.</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Санкт-Петербург, Сенная площадь</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/portrait-main.jpg | https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/portrait-close.jpg</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Индивидуальные</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Меньше месяца</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Не выдаётся</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Взрослые</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Онлайн с преподавателем</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Новички</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Удалённо | У клиента</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Первая встреча 30 минут|1500||за услугу
-Своя услуга|Занятие 90 минут|4500||за услугу
-Своя услуга|Пакет из 3 занятий|12000||за услугу</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>IT, бизнес</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Бизнес и финансы</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Мужчина</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>4–6 лет</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>edu-02-dlya-raboty</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Обучение, курсы</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Профессии и бизнес</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Нейросети для офисной работы: ChatGPT и Claude</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
         <is>
           <t>Отчёт к пятнице, письмо клиенту, которое надо написать «нормально», презентация к понедельнику и таблица, в которой опять всё съехало. Нейросети умеют забирать половину этого, но большинство коллег пользуются ими как поисковиком: спросил, получил воду, закрыл.
 Привет, я Лев, консультант по внедрению ИИ. Пользуюсь нейросетями каждый день с 2022 года. Занятия строю от вашей профессии и ваших задач, а не от «возможностей технологии».
@@ -2235,77 +1640,77 @@
 Онлайн по всей России, в Петербурге можно очно.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>4500</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Санкт-Петербург, Сенная площадь</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/portrait-close.jpg | https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/portrait-main.jpg</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/casual-church.jpg</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Индивидуальные</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Меньше месяца</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Не выдаётся</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Взрослые</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Онлайн с преподавателем</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Новички</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Удалённо | У клиента</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Своя услуга|Диагностика 30 минут|1500||за услугу
 Своя услуга|Занятие 90 минут|4500||за услугу
@@ -2313,74 +1718,74 @@
 Своя услуга|Сопровождение на месяц|15000||за услугу</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>IT, бизнес</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Бизнес и финансы</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Другое</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Мужчина</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>4–6 лет</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>edu-03-vaibkoding</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Предложение услуг</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Обучение, курсы</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Профессии и бизнес</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Вайбкодинг: Claude Code и Codex под ваши задачи</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Вы уже уверенно пользуетесь текстовыми нейросетями и упёрлись в потолок: хочется не переписку в чате, а чтобы модель сама делала работу в ваших файлах и программах.
 Это другой уровень инструментов: Claude Code и Codex. Они запускаются у вас на компьютере, видят ваши файлы, правят их, запускают проверки и повторяют, пока не получится. Программистом для этого быть не нужно. Нужно понимать, как ставить задачу и как проверять результат.
@@ -2399,119 +1804,119 @@
 Онлайн по всей России, в Петербурге можно очно.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>4500</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Санкт-Петербург, Сенная площадь</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/portrait-close.jpg | https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/expo-main.jpg</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/casual-sea.jpg</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Индивидуальные</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Меньше месяца</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Не выдаётся</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Взрослые</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Онлайн с преподавателем</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Опытные</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Удалённо | У клиента</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Своя услуга|Занятие 90 минут|4500||за услугу
 Своя услуга|Пакет из 3 занятий|12000||за услугу
 Своя услуга|Сопровождение на месяц|15000||за услугу</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>IT, бизнес</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Программирование</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Другое</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Мужчина</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>4–6 лет</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
@@ -2522,7 +1927,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2712,7 +2117,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/portrait-main.jpg | https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/portrait-close.jpg</t>
+          <t>https://raw.githubusercontent.com/lovecof/avi-feed/main/photos/casual-city.jpg</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
